--- a/MLD01e_Results/Table01_DataSummaryForKnowledge_v1.xlsx
+++ b/MLD01e_Results/Table01_DataSummaryForKnowledge_v1.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29325"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_6B15F30F56790E0E62355476585DCE3A87472695" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B30DF9D4-7A03-4800-850E-EDA49D355FF9}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ccceaaab575c7926/MLD01_Article/MLD01e_Results/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_6B15F30F56790E0E62355476585DCE3A87472695" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B073237-DAE7-7146-993E-0BCBA1AFE304}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -256,7 +261,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -312,7 +317,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -325,6 +330,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -613,9 +622,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I66"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="42.1640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -641,7 +653,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -670,7 +682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -699,7 +711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -728,7 +740,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -757,7 +769,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -786,7 +798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -815,7 +827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -844,7 +856,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -873,7 +885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -902,7 +914,7 @@
         <v>0.8571428571428571</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -931,7 +943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -960,7 +972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -989,7 +1001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
@@ -1018,7 +1030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -1047,7 +1059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
@@ -1076,7 +1088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
@@ -1105,7 +1117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
@@ -1134,7 +1146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
@@ -1163,7 +1175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
@@ -1192,7 +1204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
@@ -1221,7 +1233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -1250,7 +1262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
@@ -1279,7 +1291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>30</v>
       </c>
@@ -1308,7 +1320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>31</v>
       </c>
@@ -1337,7 +1349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>32</v>
       </c>
@@ -1366,7 +1378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>33</v>
       </c>
@@ -1395,7 +1407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
@@ -1424,7 +1436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
@@ -1453,7 +1465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>36</v>
       </c>
@@ -1482,7 +1494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -1511,7 +1523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>38</v>
       </c>
@@ -1540,7 +1552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>39</v>
       </c>
@@ -1569,7 +1581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
@@ -1598,7 +1610,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>41</v>
       </c>
@@ -1627,7 +1639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>42</v>
       </c>
@@ -1656,7 +1668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>43</v>
       </c>
@@ -1685,7 +1697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>44</v>
       </c>
@@ -1714,7 +1726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>45</v>
       </c>
@@ -1743,7 +1755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>46</v>
       </c>
@@ -1772,7 +1784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>47</v>
       </c>
@@ -1801,7 +1813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>48</v>
       </c>
@@ -1830,7 +1842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>49</v>
       </c>
@@ -1859,7 +1871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>50</v>
       </c>
@@ -1888,7 +1900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>51</v>
       </c>
@@ -1917,7 +1929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>52</v>
       </c>
@@ -1946,7 +1958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>53</v>
       </c>
@@ -1975,7 +1987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>54</v>
       </c>
@@ -2004,7 +2016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>55</v>
       </c>
@@ -2033,7 +2045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>56</v>
       </c>
@@ -2062,7 +2074,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>57</v>
       </c>
@@ -2091,7 +2103,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>58</v>
       </c>
@@ -2120,7 +2132,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>59</v>
       </c>
@@ -2149,7 +2161,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>60</v>
       </c>
@@ -2178,7 +2190,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>61</v>
       </c>
@@ -2207,7 +2219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>62</v>
       </c>
@@ -2236,7 +2248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>63</v>
       </c>
@@ -2265,7 +2277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>64</v>
       </c>
@@ -2294,7 +2306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>65</v>
       </c>
@@ -2323,7 +2335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>66</v>
       </c>
@@ -2352,7 +2364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>67</v>
       </c>
@@ -2381,7 +2393,7 @@
         <v>3900000</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>68</v>
       </c>
@@ -2410,7 +2422,7 @@
         <v>7200000</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>69</v>
       </c>
@@ -2439,7 +2451,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>70</v>
       </c>
@@ -2468,7 +2480,7 @@
         <v>99000000</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>71</v>
       </c>
@@ -2497,7 +2509,7 @@
         <v>99200000</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>72</v>
       </c>
